--- a/data/merged/2026-09-23/MERGED_IT_Robot-Vacuum_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_IT_Robot-Vacuum_2026-09-23.xlsx
@@ -3383,13 +3383,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3427,13 +3427,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3515,13 +3515,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3559,13 +3559,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3603,13 +3603,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3647,13 +3647,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3829,7 +3829,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3873,7 +3873,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3911,13 +3911,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3955,13 +3955,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4087,13 +4087,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4131,13 +4131,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4225,7 +4225,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4269,7 +4269,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4401,7 +4401,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4445,7 +4445,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4483,13 +4483,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4527,13 +4527,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4615,13 +4615,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4659,13 +4659,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4747,13 +4747,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4835,13 +4835,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4967,13 +4967,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5011,13 +5011,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5407,13 +5407,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5474,50 +5474,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5859,7 +5815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -6380,7 +6336,7 @@
       <c r="B3" s="13"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>B0C78DVSYP</t>
+          <t>B0CTCXKL52</t>
         </is>
       </c>
       <c r="D3" s="14"/>
@@ -6393,23 +6349,23 @@
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>DREAME 4x Panni mocio di ricambio(×2 Paia) compatibili con X40Master/L10sUltraGen2/L50ProUltra/X50Master/L40sProUltra/L40Ultr</t>
+          <t>XIAOMI X20+ Robot aspirapolvere con lavaggio e panno sollevabile, 6000 PasEvitamento ostacoli LDS, auto-pulizia, asciugatur</t>
         </is>
       </c>
       <c r="I3" s="14"/>
       <c r="J3" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0C78DVSYP?psc=1</t>
+          <t>https://www.amazon.it/dp/B0CTCXKL52?psc=1</t>
         </is>
       </c>
       <c r="K3" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71wCGkM+anL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61+Y7BWWOlL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>B0C78DVSYP</t>
+          <t>B0CTCXKL52</t>
         </is>
       </c>
       <c r="M3" s="1"/>
@@ -6426,17 +6382,17 @@
       <c r="X3" s="15"/>
       <c r="Y3"/>
       <c r="Z3" s="4">
-        <v>15.16</v>
+        <v>245.89</v>
       </c>
       <c r="AA3"/>
       <c r="AB3"/>
       <c r="AC3"/>
       <c r="AD3" s="19">
-        <v>606</v>
+        <v>5446</v>
       </c>
       <c r="AE3"/>
       <c r="AF3" s="20">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG3" s="21">
         <v>0</v>
@@ -6488,7 +6444,7 @@
       <c r="B4" s="13"/>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>B0CTCXKL52</t>
+          <t>B0DGQVLY99</t>
         </is>
       </c>
       <c r="D4" s="14"/>
@@ -6501,23 +6457,23 @@
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>XIAOMI X20+ Robot aspirapolvere con lavaggio e panno sollevabile, 6000 PasEvitamento ostacoli LDS, auto-pulizia, asciugatur</t>
+          <t>Tapo RV30 Max Plus Robot Aspirapolvere Lavapavimenti 5300Pa LiDAR Base 3LsPer Casa e Animali, Svuotamento Automatico 3L, Na</t>
         </is>
       </c>
       <c r="I4" s="14"/>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0CTCXKL52?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DGQVLY99?psc=1</t>
         </is>
       </c>
       <c r="K4" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61+Y7BWWOlL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71RZtXsJInL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L4" s="14" t="inlineStr">
         <is>
-          <t>B0CTCXKL52</t>
+          <t>B0DGQVLY99</t>
         </is>
       </c>
       <c r="M4" s="1"/>
@@ -6533,18 +6489,16 @@
       <c r="W4" s="15"/>
       <c r="X4" s="15"/>
       <c r="Y4"/>
-      <c r="Z4" s="4">
-        <v>245.89</v>
-      </c>
+      <c r="Z4" s="4"/>
       <c r="AA4"/>
       <c r="AB4"/>
       <c r="AC4"/>
       <c r="AD4" s="19">
-        <v>5446</v>
+        <v>6911</v>
       </c>
       <c r="AE4"/>
       <c r="AF4" s="20">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AG4" s="21">
         <v>0</v>
@@ -6596,7 +6550,7 @@
       <c r="B5" s="13"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>B0DGQVLY99</t>
+          <t>B0DHKM58LV</t>
         </is>
       </c>
       <c r="D5" s="14"/>
@@ -6609,23 +6563,23 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>Tapo RV30 Max Plus Robot Aspirapolvere Lavapavimenti 5300Pa LiDAR Base 3LsPer Casa e Animali, Svuotamento Automatico 3L, Na</t>
+          <t>Tapo RV20 Max Plus Robot Aspirapolvere Lavapavimenti 5300Pa LiDAR 83mmsPer Casa e Animali, Svuotamento Automatico 3L, Navig</t>
         </is>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DGQVLY99?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DHKM58LV?psc=1</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71RZtXsJInL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71jEf9a4LnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>B0DGQVLY99</t>
+          <t>B0DHKM58LV</t>
         </is>
       </c>
       <c r="M5" s="1"/>
@@ -6641,16 +6595,18 @@
       <c r="W5" s="15"/>
       <c r="X5" s="15"/>
       <c r="Y5"/>
-      <c r="Z5" s="4"/>
+      <c r="Z5" s="4">
+        <v>131.14</v>
+      </c>
       <c r="AA5"/>
       <c r="AB5"/>
       <c r="AC5"/>
       <c r="AD5" s="19">
-        <v>6911</v>
+        <v>4967</v>
       </c>
       <c r="AE5"/>
       <c r="AF5" s="20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AG5" s="21">
         <v>0</v>
@@ -6702,7 +6658,7 @@
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>B0DHKM58LV</t>
+          <t>B0DPB7RN2L</t>
         </is>
       </c>
       <c r="D6" s="14"/>
@@ -6715,23 +6671,23 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Tapo RV20 Max Plus Robot Aspirapolvere Lavapavimenti 5300Pa LiDAR 83mmsPer Casa e Animali, Svuotamento Automatico 3L, Navig</t>
+          <t>dreame X50 Ultra Complete Robot Aspirapolvere Lavapavimenti, 20.000 PasRileva Ostacoli con IA, Navigazione 360°, Pulizia so</t>
         </is>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DHKM58LV?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DPB7RN2L?psc=1</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71jEf9a4LnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71uia0AyolL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>B0DHKM58LV</t>
+          <t>B0DPB7RN2L</t>
         </is>
       </c>
       <c r="M6" s="1"/>
@@ -6748,17 +6704,17 @@
       <c r="X6" s="15"/>
       <c r="Y6"/>
       <c r="Z6" s="4">
-        <v>131.14</v>
+        <v>613.93</v>
       </c>
       <c r="AA6"/>
       <c r="AB6"/>
       <c r="AC6"/>
       <c r="AD6" s="19">
-        <v>4967</v>
+        <v>1854</v>
       </c>
       <c r="AE6"/>
       <c r="AF6" s="20">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG6" s="21">
         <v>0</v>
@@ -6810,7 +6766,7 @@
       <c r="B7" s="13"/>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>B0DPB7RN2L</t>
+          <t>B0DPZTS99T</t>
         </is>
       </c>
       <c r="D7" s="14"/>
@@ -6823,23 +6779,23 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>dreame X50 Ultra Complete Robot Aspirapolvere Lavapavimenti, 20.000 PasRileva Ostacoli con IA, Navigazione 360°, Pulizia so</t>
+          <t>MOVA P50 Pro Ultra Robot Aspirapolvere, Biancos19.000 Pa, Pulizia Angolo-Bordo, Autopulizia A 75°C, Svuotamento E Riempimen</t>
         </is>
       </c>
       <c r="I7" s="14"/>
       <c r="J7" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DPB7RN2L?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DPZTS99T?psc=1</t>
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71uia0AyolL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61h0GDNMI4L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>B0DPB7RN2L</t>
+          <t>B0DPZTS99T</t>
         </is>
       </c>
       <c r="M7" s="1"/>
@@ -6856,13 +6812,13 @@
       <c r="X7" s="15"/>
       <c r="Y7"/>
       <c r="Z7" s="4">
-        <v>613.93</v>
+        <v>351.64</v>
       </c>
       <c r="AA7"/>
       <c r="AB7"/>
       <c r="AC7"/>
       <c r="AD7" s="19">
-        <v>1854</v>
+        <v>743</v>
       </c>
       <c r="AE7"/>
       <c r="AF7" s="20">
@@ -6918,7 +6874,7 @@
       <c r="B8" s="13"/>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>B0DPZTS99T</t>
+          <t>B0DSZXC512</t>
         </is>
       </c>
       <c r="D8" s="14"/>
@@ -6931,23 +6887,23 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>MOVA P50 Pro Ultra Robot Aspirapolvere, Biancos19.000 Pa, Pulizia Angolo-Bordo, Autopulizia A 75°C, Svuotamento E Riempimen</t>
+          <t>roborock Q10 S5 Set Robot Aspirapolvere 10.000Pa, Panno Sollevabile, BiancosPulizia VibraRise 2.0(3000 volte/min), Anti-gro</t>
         </is>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DPZTS99T?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DSZXC512?psc=1</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61h0GDNMI4L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61DA4yhQb2L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>B0DPZTS99T</t>
+          <t>B0DSZXC512</t>
         </is>
       </c>
       <c r="M8" s="1"/>
@@ -6963,18 +6919,16 @@
       <c r="W8" s="15"/>
       <c r="X8" s="15"/>
       <c r="Y8"/>
-      <c r="Z8" s="4">
-        <v>351.64</v>
-      </c>
+      <c r="Z8" s="4"/>
       <c r="AA8"/>
       <c r="AB8"/>
       <c r="AC8"/>
       <c r="AD8" s="19">
-        <v>743</v>
+        <v>2920</v>
       </c>
       <c r="AE8"/>
       <c r="AF8" s="20">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AG8" s="21">
         <v>0</v>
@@ -7026,7 +6980,7 @@
       <c r="B9" s="13"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>B0DSZXC512</t>
+          <t>B0DV9TBKM1</t>
         </is>
       </c>
       <c r="D9" s="14"/>
@@ -7039,23 +6993,23 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>roborock Q10 S5 Set Robot Aspirapolvere 10.000Pa, Panno Sollevabile, BiancosPulizia VibraRise 2.0(3000 volte/min), Anti-gro</t>
+          <t>iRobot Roomba 105 Combo robot aspirapolvere lavapavimenti, 7.000 PasCon stazione autosvuotamento, navigazione ClearView LiD</t>
         </is>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DSZXC512?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DV9TBKM1?psc=1</t>
         </is>
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61DA4yhQb2L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71ge+TRWY0L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>B0DSZXC512</t>
+          <t>B0DV9TBKM1</t>
         </is>
       </c>
       <c r="M9" s="1"/>
@@ -7076,11 +7030,11 @@
       <c r="AB9"/>
       <c r="AC9"/>
       <c r="AD9" s="19">
-        <v>2920</v>
+        <v>10765</v>
       </c>
       <c r="AE9"/>
       <c r="AF9" s="20">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AG9" s="21">
         <v>0</v>
@@ -7132,7 +7086,7 @@
       <c r="B10" s="13"/>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>B0DV9TBKM1</t>
+          <t>B0DWK8GJZX</t>
         </is>
       </c>
       <c r="D10" s="14"/>
@@ -7145,23 +7099,23 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>iRobot Roomba 105 Combo robot aspirapolvere lavapavimenti, 7.000 PasCon stazione autosvuotamento, navigazione ClearView LiD</t>
+          <t>roborock Q7 L5+ Robot Aspirapolvere con Stazione Svuotamento Automaticos8.000 Pa, Quantità d'acqua Regolabile per il Lavagg</t>
         </is>
       </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DV9TBKM1?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DWK8GJZX?psc=1</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71ge+TRWY0L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/518ZZDibQUL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>B0DV9TBKM1</t>
+          <t>B0DWK8GJZX</t>
         </is>
       </c>
       <c r="M10" s="1"/>
@@ -7182,11 +7136,11 @@
       <c r="AB10"/>
       <c r="AC10"/>
       <c r="AD10" s="19">
-        <v>10765</v>
+        <v>3272</v>
       </c>
       <c r="AE10"/>
       <c r="AF10" s="20">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AG10" s="21">
         <v>0</v>
@@ -7238,7 +7192,7 @@
       <c r="B11" s="13"/>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>B0DWK8GJZX</t>
+          <t>B0DZ64GW9Z</t>
         </is>
       </c>
       <c r="D11" s="14"/>
@@ -7251,23 +7205,23 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>roborock Q7 L5+ Robot Aspirapolvere con Stazione Svuotamento Automaticos8.000 Pa, Quantità d'acqua Regolabile per il Lavagg</t>
+          <t>ECOVACS T80 OMNI Robot Aspirapolvere Lavapavimenti 18000 Pa OZMO ROLLERsZeroTangle Generation 3.0, Lavaggio Mocio con Acqua</t>
         </is>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DWK8GJZX?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DZ64GW9Z?psc=1</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/518ZZDibQUL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61DTY2iTgGL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>B0DWK8GJZX</t>
+          <t>B0DZ64GW9Z</t>
         </is>
       </c>
       <c r="M11" s="1"/>
@@ -7288,11 +7242,11 @@
       <c r="AB11"/>
       <c r="AC11"/>
       <c r="AD11" s="19">
-        <v>3272</v>
+        <v>762</v>
       </c>
       <c r="AE11"/>
       <c r="AF11" s="20">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AG11" s="21">
         <v>0</v>
@@ -7344,7 +7298,7 @@
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>B0DZ64GW9Z</t>
+          <t>B0F4JZNGT8</t>
         </is>
       </c>
       <c r="D12" s="14"/>
@@ -7357,23 +7311,23 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>ECOVACS T80 OMNI Robot Aspirapolvere Lavapavimenti 18000 Pa OZMO ROLLERsZeroTangle Generation 3.0, Lavaggio Mocio con Acqua</t>
+          <t>XIAOMI H40 Robot aspirapolvere con stazione auto-svuotamento, 10000 PasStazione compatta sacchetto 4L, fino a 90 giorni sen</t>
         </is>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DZ64GW9Z?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F4JZNGT8?psc=1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61DTY2iTgGL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61h6FZILm2L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>B0DZ64GW9Z</t>
+          <t>B0F4JZNGT8</t>
         </is>
       </c>
       <c r="M12" s="1"/>
@@ -7389,16 +7343,18 @@
       <c r="W12" s="15"/>
       <c r="X12" s="15"/>
       <c r="Y12"/>
-      <c r="Z12" s="4"/>
+      <c r="Z12" s="4">
+        <v>182.86</v>
+      </c>
       <c r="AA12"/>
       <c r="AB12"/>
       <c r="AC12"/>
       <c r="AD12" s="19">
-        <v>762</v>
+        <v>439</v>
       </c>
       <c r="AE12"/>
       <c r="AF12" s="20">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AG12" s="21">
         <v>0</v>
@@ -7450,7 +7406,7 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B0F4JZNGT8</t>
+          <t>B0F53MJY8T</t>
         </is>
       </c>
       <c r="D13" s="14"/>
@@ -7463,23 +7419,23 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>XIAOMI H40 Robot aspirapolvere con stazione auto-svuotamento, 10000 PasStazione compatta sacchetto 4L, fino a 90 giorni sen</t>
+          <t>dreame L40 Ultra AE Robot Aspirapolvere, Lavaggio Panno 75°CsAspir. 19.000 Pa, Spazzola TriCut, Tecnologia MopExtend, Aggir</t>
         </is>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F4JZNGT8?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F53MJY8T?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61h6FZILm2L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61Oewwp7QtL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B0F4JZNGT8</t>
+          <t>B0F53MJY8T</t>
         </is>
       </c>
       <c r="M13" s="1"/>
@@ -7496,13 +7452,13 @@
       <c r="X13" s="15"/>
       <c r="Y13"/>
       <c r="Z13" s="4">
-        <v>182.86</v>
+        <v>327.05</v>
       </c>
       <c r="AA13"/>
       <c r="AB13"/>
       <c r="AC13"/>
       <c r="AD13" s="19">
-        <v>439</v>
+        <v>2664</v>
       </c>
       <c r="AE13"/>
       <c r="AF13" s="20">
@@ -7558,7 +7514,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B0F53MJY8T</t>
+          <t>B0FBG6V2LG</t>
         </is>
       </c>
       <c r="D14" s="14"/>
@@ -7571,23 +7527,23 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>dreame L40 Ultra AE Robot Aspirapolvere, Lavaggio Panno 75°CsAspir. 19.000 Pa, Spazzola TriCut, Tecnologia MopExtend, Aggir</t>
+          <t>EUREKA E20 Evo Plus Robot Aspirapolvere e Lavapavimenti, 10.000Pa, Anti-Groviglio, 180min Autonomia, Mappatura LDS, Base Senz</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F53MJY8T?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FBG6V2LG?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61Oewwp7QtL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71Du2Zv+GrL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B0F53MJY8T</t>
+          <t>B0FBG6V2LG</t>
         </is>
       </c>
       <c r="M14" s="1"/>
@@ -7604,17 +7560,17 @@
       <c r="X14" s="15"/>
       <c r="Y14"/>
       <c r="Z14" s="4">
-        <v>327.05</v>
+        <v>163.93</v>
       </c>
       <c r="AA14"/>
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14" s="19">
-        <v>2664</v>
+        <v>97</v>
       </c>
       <c r="AE14"/>
       <c r="AF14" s="20">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG14" s="21">
         <v>0</v>
@@ -7666,7 +7622,7 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B0FBG6V2LG</t>
+          <t>B0FBGXW79K</t>
         </is>
       </c>
       <c r="D15" s="14"/>
@@ -7679,23 +7635,23 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>EUREKA E20 Evo Plus Robot Aspirapolvere e Lavapavimenti, 10.000Pa, Anti-Groviglio, 180min Autonomia, Mappatura LDS, Base Senz</t>
+          <t>dreame D20 Pro Plus Robot Aspirapolvere Lavapavimenti, DuoBrush per Pelis13.000 Pa, Pulizia Angoli, Stazione Svuotamento Au</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FBG6V2LG?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FBGXW79K?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71Du2Zv+GrL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61AWpU4EwAL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B0FBG6V2LG</t>
+          <t>B0FBGXW79K</t>
         </is>
       </c>
       <c r="M15" s="1"/>
@@ -7712,17 +7668,17 @@
       <c r="X15" s="15"/>
       <c r="Y15"/>
       <c r="Z15" s="4">
-        <v>163.93</v>
+        <v>163.11</v>
       </c>
       <c r="AA15"/>
       <c r="AB15"/>
       <c r="AC15"/>
       <c r="AD15" s="19">
-        <v>97</v>
+        <v>1028</v>
       </c>
       <c r="AE15"/>
       <c r="AF15" s="20">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG15" s="21">
         <v>0</v>
@@ -7774,7 +7730,7 @@
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>B0FBGXW79K</t>
+          <t>B0FC2VSX1R</t>
         </is>
       </c>
       <c r="D16" s="14"/>
@@ -7787,23 +7743,23 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>dreame D20 Pro Plus Robot Aspirapolvere Lavapavimenti, DuoBrush per Pelis13.000 Pa, Pulizia Angoli, Stazione Svuotamento Au</t>
+          <t>roborock Saros 10R Set Robot Aspirapolvere Lavapavimenti 22.000Pa, 7,98 cmsAntigroviglio, Telaio AdaptiLift, Rimozione Auto</t>
         </is>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FBGXW79K?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FC2VSX1R?psc=1</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61AWpU4EwAL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61Sp5FUK9FL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>B0FBGXW79K</t>
+          <t>B0FC2VSX1R</t>
         </is>
       </c>
       <c r="M16" s="1"/>
@@ -7819,18 +7775,16 @@
       <c r="W16" s="15"/>
       <c r="X16" s="15"/>
       <c r="Y16"/>
-      <c r="Z16" s="4">
-        <v>163.11</v>
-      </c>
+      <c r="Z16" s="4"/>
       <c r="AA16"/>
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16" s="19">
-        <v>1028</v>
+        <v>1777</v>
       </c>
       <c r="AE16"/>
       <c r="AF16" s="20">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AG16" s="21">
         <v>0</v>
@@ -7882,7 +7836,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>B0FC2VSX1R</t>
+          <t>B0FDLDM33M</t>
         </is>
       </c>
       <c r="D17" s="14"/>
@@ -7895,23 +7849,23 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>roborock Saros 10R Set Robot Aspirapolvere Lavapavimenti 22.000Pa, 7,98 cmsAntigroviglio, Telaio AdaptiLift, Rimozione Auto</t>
+          <t>MOVA E40 Ultra Robot Aspirapolvere, Biancos19000Pa, Tecnologia Mocio MaxiReach, Spazzola Laterale Antigroviglio, Stazione A</t>
         </is>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FC2VSX1R?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FDLDM33M?psc=1</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61Sp5FUK9FL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61PLSniytTL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>B0FC2VSX1R</t>
+          <t>B0FDLDM33M</t>
         </is>
       </c>
       <c r="M17" s="1"/>
@@ -7932,11 +7886,11 @@
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17" s="19">
-        <v>1777</v>
+        <v>520</v>
       </c>
       <c r="AE17"/>
       <c r="AF17" s="20">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AG17" s="21">
         <v>0</v>
@@ -7988,7 +7942,7 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B0FDLDM33M</t>
+          <t>B0FFGQ7L2T</t>
         </is>
       </c>
       <c r="D18" s="14"/>
@@ -8001,23 +7955,23 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>MOVA E40 Ultra Robot Aspirapolvere, Biancos19000Pa, Tecnologia Mocio MaxiReach, Spazzola Laterale Antigroviglio, Stazione A</t>
+          <t>roborock Qrevo Curv 2 Pro Robot Aspirapolvere Lavapavimenti, LDS Retrattiles7,98 cm, 25.000 Pa, Telaio AdaptiLift, Zero-Gro</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FDLDM33M?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FFGQ7L2T?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61PLSniytTL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61lhiSiiW9L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B0FDLDM33M</t>
+          <t>B0FFGQ7L2T</t>
         </is>
       </c>
       <c r="M18" s="1"/>
@@ -8038,11 +7992,11 @@
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18" s="19">
-        <v>520</v>
+        <v>1530</v>
       </c>
       <c r="AE18"/>
       <c r="AF18" s="20">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AG18" s="21">
         <v>0</v>
@@ -8094,7 +8048,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B0FFGQ7L2T</t>
+          <t>B0FHHYQ58Q</t>
         </is>
       </c>
       <c r="D19" s="14"/>
@@ -8107,23 +8061,23 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>roborock Qrevo Curv 2 Pro Robot Aspirapolvere Lavapavimenti, LDS Retrattiles7,98 cm, 25.000 Pa, Telaio AdaptiLift, Zero-Gro</t>
+          <t>dreame Aqua10 Ultra Roller Complete Robot Aspirapolvere, Aspir. 30.000 PasMocio AquaRoll, Superamento Ostacoli 8 cm, Protez</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FFGQ7L2T?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FHHYQ58Q?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61lhiSiiW9L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/719E8Elku9L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B0FFGQ7L2T</t>
+          <t>B0FHHYQ58Q</t>
         </is>
       </c>
       <c r="M19" s="1"/>
@@ -8144,11 +8098,11 @@
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19" s="19">
-        <v>1530</v>
+        <v>556</v>
       </c>
       <c r="AE19"/>
       <c r="AF19" s="20">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG19" s="21">
         <v>0</v>
@@ -8200,7 +8154,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0FHHYQ58Q</t>
+          <t>B0FHWP5Y6P</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -8213,23 +8167,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>dreame Aqua10 Ultra Roller Complete Robot Aspirapolvere, Aspir. 30.000 PasMocio AquaRoll, Superamento Ostacoli 8 cm, Protez</t>
+          <t>ECOVACS X11 OMNICYCLONE Robot Aspirapolvere Lavapavimenti 19500 PasBoost di Potenza Ultrarapido, OZMO ROLLER Gen 2.0, Altez</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FHHYQ58Q?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FHWP5Y6P?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/719E8Elku9L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81n8UEz9tuL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0FHHYQ58Q</t>
+          <t>B0FHWP5Y6P</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -8245,16 +8199,18 @@
       <c r="W20" s="15"/>
       <c r="X20" s="15"/>
       <c r="Y20"/>
-      <c r="Z20" s="4"/>
+      <c r="Z20" s="4">
+        <v>531.97</v>
+      </c>
       <c r="AA20"/>
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20" s="19">
-        <v>556</v>
+        <v>606</v>
       </c>
       <c r="AE20"/>
       <c r="AF20" s="20">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AG20" s="21">
         <v>0</v>
@@ -8306,7 +8262,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0FHWP5Y6P</t>
+          <t>B0FL2JGPYH</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -8319,23 +8275,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>ECOVACS X11 OMNICYCLONE Robot Aspirapolvere Lavapavimenti 19500 PasBoost di Potenza Ultrarapido, OZMO ROLLER Gen 2.0, Altez</t>
+          <t>Cecotec Robot Aspirapolvere con Navigazione Giroscopica e App Conga M10 X-Treme. 2000Pa, Spazza, Aspira, Lava e Passa il Moci</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FHWP5Y6P?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FL2JGPYH?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81n8UEz9tuL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/9189DpGCbIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0FHWP5Y6P</t>
+          <t>B0FL2JGPYH</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -8352,17 +8308,17 @@
       <c r="X21" s="15"/>
       <c r="Y21"/>
       <c r="Z21" s="4">
-        <v>531.97</v>
+        <v>59.75</v>
       </c>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21" s="19">
-        <v>606</v>
+        <v>621</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" s="20">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AG21" s="21">
         <v>0</v>
@@ -8414,7 +8370,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0FL2JGPYH</t>
+          <t>B0FNWFTJKQ</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -8427,23 +8383,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Robot Aspirapolvere con Navigazione Giroscopica e App Conga M10 X-Treme. 2000Pa, Spazza, Aspira, Lava e Passa il Moci</t>
+          <t>Lefant M210P Robot Aspirapolvere 2200Pa Ultra Sottile 7,8cm, NerosDesign senza spazzola centrale per ridurre i grovigli di</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FL2JGPYH?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FNWFTJKQ?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/9189DpGCbIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61R08mDJ-PL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0FL2JGPYH</t>
+          <t>B0FNWFTJKQ</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -8459,18 +8415,16 @@
       <c r="W22" s="15"/>
       <c r="X22" s="15"/>
       <c r="Y22"/>
-      <c r="Z22" s="4">
-        <v>59.75</v>
-      </c>
+      <c r="Z22" s="4"/>
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22" s="19">
-        <v>621</v>
+        <v>10395</v>
       </c>
       <c r="AE22"/>
       <c r="AF22" s="20">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AG22" s="21">
         <v>0</v>
@@ -8522,7 +8476,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0FNWFTJKQ</t>
+          <t>B0FXXCFT8Z</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -8535,23 +8489,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Lefant M210P Robot Aspirapolvere 2200Pa Ultra Sottile 7,8cm, NerosDesign senza spazzola centrale per ridurre i grovigli di</t>
+          <t>Lefant M5 Max Robot Aspirapolvere Lavapavimenti con Rullo 25000PasRullo Autopulente, Anti-Groviglio 100%, Lavaggio Acqua Vi</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FNWFTJKQ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FXXCFT8Z?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61R08mDJ-PL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71apWwSX4-L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0FNWFTJKQ</t>
+          <t>B0FXXCFT8Z</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -8572,11 +8526,11 @@
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23" s="19">
-        <v>10395</v>
+        <v>2324</v>
       </c>
       <c r="AE23"/>
       <c r="AF23" s="20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG23" s="21">
         <v>0</v>
@@ -8628,7 +8582,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0FXXCFT8Z</t>
+          <t>B0G4NBBZLG</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -8641,23 +8595,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Lefant M5 Max Robot Aspirapolvere Lavapavimenti con Rullo 25000PasRullo Autopulente, Anti-Groviglio 100%, Lavaggio Acqua Vi</t>
+          <t>roborock Saros 20 Robot Aspirapolvere Lavapavimenti 36.000Pa, 7,95cmsSupera Ostacoli da 8,8cm, Anti-Groviglio, Evita Oltre</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FXXCFT8Z?psc=1</t>
+          <t>https://www.amazon.it/dp/B0G4NBBZLG?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71apWwSX4-L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61575fRbYFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0FXXCFT8Z</t>
+          <t>B0G4NBBZLG</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -8678,11 +8632,11 @@
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24" s="19">
-        <v>2324</v>
+        <v>431</v>
       </c>
       <c r="AE24"/>
       <c r="AF24" s="20">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG24" s="21">
         <v>0</v>
@@ -8734,7 +8688,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0G4NBBZLG</t>
+          <t>B0G81F3HSR</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -8747,23 +8701,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>roborock Saros 20 Robot Aspirapolvere Lavapavimenti 36.000Pa, 7,95cmsSupera Ostacoli da 8,8cm, Anti-Groviglio, Evita Oltre</t>
+          <t>Lefant M3 Max Robot Aspirapolvere Lavapavimenti con Mappatura 20.000PasPulizia Automatica Mop, 8 Settimane Senza Pulizia, S</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0G4NBBZLG?psc=1</t>
+          <t>https://www.amazon.it/dp/B0G81F3HSR?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61575fRbYFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71FDvNkpTPL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0G4NBBZLG</t>
+          <t>B0G81F3HSR</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -8784,7 +8738,7 @@
       <c r="AB25"/>
       <c r="AC25"/>
       <c r="AD25" s="19">
-        <v>431</v>
+        <v>3362</v>
       </c>
       <c r="AE25"/>
       <c r="AF25" s="20">
@@ -8840,7 +8794,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0G81F3HSR</t>
+          <t>B0GHN9DR1C</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -8853,23 +8807,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Lefant M3 Max Robot Aspirapolvere Lavapavimenti con Mappatura 20.000PasPulizia Automatica Mop, 8 Settimane Senza Pulizia, S</t>
+          <t>roborock Qrevo S Pro Robot Aspirapolvere Lavapavimenti, Lavaggio Panno 75°CsAsciugatura Aria Calda 45°C, 18.500Pa, Antigrov</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0G81F3HSR?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GHN9DR1C?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71FDvNkpTPL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61Sk4jG6C4L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0G81F3HSR</t>
+          <t>B0GHN9DR1C</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -8890,11 +8844,11 @@
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26" s="19">
-        <v>3362</v>
+        <v>4033</v>
       </c>
       <c r="AE26"/>
       <c r="AF26" s="20">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG26" s="21">
         <v>0</v>
@@ -8946,7 +8900,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0GHN9DR1C</t>
+          <t>B0GJRWS8BQ</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -8959,23 +8913,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>roborock Qrevo S Pro Robot Aspirapolvere Lavapavimenti, Lavaggio Panno 75°CsAsciugatura Aria Calda 45°C, 18.500Pa, Antigrov</t>
+          <t>R11 Robot Aspirapolvere Lavapavimenti con Mappatura, 20000Pa, Stazione di Autosvuotamento 120 Giorni, Navigazione Lidar, WiFi</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GHN9DR1C?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GJRWS8BQ?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61Sk4jG6C4L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71+HO6GsuVL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0GHN9DR1C</t>
+          <t>B0GJRWS8BQ</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -8996,11 +8950,11 @@
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="19">
-        <v>4033</v>
+        <v>24</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG27" s="21">
         <v>0</v>
@@ -9052,7 +9006,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0GJRWS8BQ</t>
+          <t>B0GK1RD2T7</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -9065,23 +9019,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>R11 Robot Aspirapolvere Lavapavimenti con Mappatura, 20000Pa, Stazione di Autosvuotamento 120 Giorni, Navigazione Lidar, WiFi</t>
+          <t>ECOVACS T90 PRO OMNI Robot Aspirapolvere Lavapavimenti OZMO ROLLER 30000PasRicarica PowerBoost, TruEdge 3.0, Erogazione Aut</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GJRWS8BQ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GK1RD2T7?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71+HO6GsuVL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81cXtuIXJ2L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0GJRWS8BQ</t>
+          <t>B0GK1RD2T7</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -9097,16 +9051,18 @@
       <c r="W28" s="15"/>
       <c r="X28" s="15"/>
       <c r="Y28"/>
-      <c r="Z28" s="4"/>
+      <c r="Z28" s="4">
+        <v>453.28</v>
+      </c>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28"/>
       <c r="AD28" s="19">
-        <v>24</v>
+        <v>294</v>
       </c>
       <c r="AE28"/>
       <c r="AF28" s="20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG28" s="21">
         <v>0</v>
@@ -9158,7 +9114,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0GK1RD2T7</t>
+          <t>B0GKFK2L1M</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -9171,23 +9127,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>ECOVACS T90 PRO OMNI Robot Aspirapolvere Lavapavimenti OZMO ROLLER 30000PasRicarica PowerBoost, TruEdge 3.0, Erogazione Aut</t>
+          <t>Lefant M330 Plus Robot Aspirapolvere e Lavapavimenti con Mappatura dToF, 5000Pa, 150min Autonomia, Anti-Groviglio, Evita Tapp</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GK1RD2T7?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GKFK2L1M?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81cXtuIXJ2L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71xscdGZwKL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0GK1RD2T7</t>
+          <t>B0GKFK2L1M</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -9203,18 +9159,16 @@
       <c r="W29" s="15"/>
       <c r="X29" s="15"/>
       <c r="Y29"/>
-      <c r="Z29" s="4">
-        <v>453.28</v>
-      </c>
+      <c r="Z29" s="4"/>
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29" s="19">
-        <v>294</v>
+        <v>3174</v>
       </c>
       <c r="AE29"/>
       <c r="AF29" s="20">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AG29" s="21">
         <v>0</v>
@@ -9266,7 +9220,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0GKFK2L1M</t>
+          <t>B0GLNVNGHJ</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -9279,23 +9233,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Lefant M330 Plus Robot Aspirapolvere e Lavapavimenti con Mappatura dToF, 5000Pa, 150min Autonomia, Anti-Groviglio, Evita Tapp</t>
+          <t>ECOVACS X12 OMNICYCLONE Care Complete Robot Aspirapolvere LavapavimentisAspirazione da 22000 Pa, FocusJet anti-macchie, Pow</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GKFK2L1M?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GLNVNGHJ?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71xscdGZwKL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71Nj3cHYNTL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0GKFK2L1M</t>
+          <t>B0GLNVNGHJ</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -9316,11 +9270,11 @@
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="19">
-        <v>3174</v>
+        <v>79</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="20">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AG30" s="21">
         <v>0</v>
@@ -9372,7 +9326,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0GLNVNGHJ</t>
+          <t>B0GMHC87FB</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -9385,23 +9339,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>ECOVACS X12 OMNICYCLONE Care Complete Robot Aspirapolvere LavapavimentisAspirazione da 22000 Pa, FocusJet anti-macchie, Pow</t>
+          <t>roborock Qrevo Edge 2 Set Robot Aspirapolvere Lavapavimenti 25.000PasLDS Retrattile, 7,98 cm, FlexiArm, Antigroviglio, Auto</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GLNVNGHJ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GMHC87FB?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71Nj3cHYNTL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61GibzcMLqL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0GLNVNGHJ</t>
+          <t>B0GMHC87FB</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -9422,11 +9376,11 @@
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31" s="19">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AE31"/>
       <c r="AF31" s="20">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AG31" s="21">
         <v>0</v>
@@ -9478,7 +9432,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0GMHC87FB</t>
+          <t>B0GMKFQ78D</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -9491,23 +9445,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>roborock Qrevo Edge 2 Set Robot Aspirapolvere Lavapavimenti 25.000PasLDS Retrattile, 7,98 cm, FlexiArm, Antigroviglio, Auto</t>
+          <t>MOVA S70 Roller Robot Aspirapolvere, NerosRullo 27 Cm Estendibile, Base Autopulente, 28.000 Pa, Pulizia Dei Bordi, Lavaggio</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GMHC87FB?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GMKFQ78D?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61GibzcMLqL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/31LHrNdbtZL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0GMHC87FB</t>
+          <t>B0GMKFQ78D</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -9523,16 +9477,18 @@
       <c r="W32" s="15"/>
       <c r="X32" s="15"/>
       <c r="Y32"/>
-      <c r="Z32" s="4"/>
+      <c r="Z32" s="4">
+        <v>368.03</v>
+      </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32" s="19">
-        <v>335</v>
+        <v>147</v>
       </c>
       <c r="AE32"/>
       <c r="AF32" s="20">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AG32" s="21">
         <v>0</v>
@@ -9584,7 +9540,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0GMKFQ78D</t>
+          <t>B0GQFK3DD5</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -9597,23 +9553,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>MOVA S70 Roller Robot Aspirapolvere, NerosRullo 27 Cm Estendibile, Base Autopulente, 28.000 Pa, Pulizia Dei Bordi, Lavaggio</t>
+          <t>MONSGA Robot Aspirapolvere Lavapavimenti 3-in-1, 4000Pa, Autonomia 140minsAnti-groviglio, Ricarica Automatica, Controllo Ap</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GMKFQ78D?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GQFK3DD5?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/31LHrNdbtZL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71WcgmlpUtL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0GMKFQ78D</t>
+          <t>B0GQFK3DD5</t>
         </is>
       </c>
       <c r="M33" s="1"/>
@@ -9630,13 +9586,13 @@
       <c r="X33" s="15"/>
       <c r="Y33"/>
       <c r="Z33" s="4">
-        <v>368.03</v>
+        <v>114.75</v>
       </c>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33" s="19">
-        <v>147</v>
+        <v>875</v>
       </c>
       <c r="AE33"/>
       <c r="AF33" s="20">
@@ -9692,7 +9648,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0GQFK3DD5</t>
+          <t>B0GQHBTNP8</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -9705,23 +9661,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>MONSGA Robot Aspirapolvere Lavapavimenti 3-in-1, 4000Pa, Autonomia 140minsAnti-groviglio, Ricarica Automatica, Controllo Ap</t>
+          <t>Lefant M3 Robot Aspirapolvere Lavapavimenti con Mappatura 12000Pa, GrigiosPulizia Automatica Mop, 8 Settimane Senza Pulizia</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GQFK3DD5?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GQHBTNP8?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71WcgmlpUtL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/8172iDMPT7L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0GQFK3DD5</t>
+          <t>B0GQHBTNP8</t>
         </is>
       </c>
       <c r="M34" s="1"/>
@@ -9737,18 +9693,16 @@
       <c r="W34" s="15"/>
       <c r="X34" s="15"/>
       <c r="Y34"/>
-      <c r="Z34" s="4">
-        <v>114.75</v>
-      </c>
+      <c r="Z34" s="4"/>
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34"/>
       <c r="AD34" s="19">
-        <v>875</v>
+        <v>2425</v>
       </c>
       <c r="AE34"/>
       <c r="AF34" s="20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG34" s="21">
         <v>0</v>
@@ -9800,7 +9754,7 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0GQHBTNP8</t>
+          <t>B0GQT9CQ17</t>
         </is>
       </c>
       <c r="D35" s="14"/>
@@ -9813,23 +9767,23 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Lefant M3 Robot Aspirapolvere Lavapavimenti con Mappatura 12000Pa, GrigiosPulizia Automatica Mop, 8 Settimane Senza Pulizia</t>
+          <t>ECOVACS T50 OMNI Gen3 Robot Aspirapolvere Lavapavimenti 25000 PasZeroTangle Generation 3.0 Tecnologia Anti-ingombramento, A</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GQHBTNP8?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GQT9CQ17?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/8172iDMPT7L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/6146vF3XIXL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0GQHBTNP8</t>
+          <t>B0GQT9CQ17</t>
         </is>
       </c>
       <c r="M35" s="1"/>
@@ -9845,16 +9799,18 @@
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
       <c r="Y35"/>
-      <c r="Z35" s="4"/>
+      <c r="Z35" s="4">
+        <v>277.87</v>
+      </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35"/>
       <c r="AD35" s="19">
-        <v>2425</v>
+        <v>341</v>
       </c>
       <c r="AE35"/>
       <c r="AF35" s="20">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AG35" s="21">
         <v>0</v>
@@ -9906,7 +9862,7 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0GQT9CQ17</t>
+          <t>B0GQVBWMN8</t>
         </is>
       </c>
       <c r="D36" s="14"/>
@@ -9919,23 +9875,23 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>ECOVACS T50 OMNI Gen3 Robot Aspirapolvere Lavapavimenti 25000 PasZeroTangle Generation 3.0 Tecnologia Anti-ingombramento, A</t>
+          <t>iRobot Roomba® 115 Combo robot aspirapolvere lavapavimenti, 15.000 PasCompatto, aspirazione e lavaggio 2 in 1, mappatura Cl</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GQT9CQ17?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GQVBWMN8?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/6146vF3XIXL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61a+kGiU4JL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0GQT9CQ17</t>
+          <t>B0GQVBWMN8</t>
         </is>
       </c>
       <c r="M36" s="1"/>
@@ -9952,17 +9908,17 @@
       <c r="X36" s="15"/>
       <c r="Y36"/>
       <c r="Z36" s="4">
-        <v>277.87</v>
+        <v>145</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
       <c r="AC36"/>
       <c r="AD36" s="19">
-        <v>341</v>
+        <v>6468</v>
       </c>
       <c r="AE36"/>
       <c r="AF36" s="20">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AG36" s="21">
         <v>0</v>
@@ -10014,7 +9970,7 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0GQVBWMN8</t>
+          <t>B0GRV9WF91</t>
         </is>
       </c>
       <c r="D37" s="14"/>
@@ -10027,23 +9983,23 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>iRobot Roomba® 115 Combo robot aspirapolvere lavapavimenti, 15.000 PasCompatto, aspirazione e lavaggio 2 in 1, mappatura Cl</t>
+          <t>Lefant M1 Robot Aspirapolvere Lavapavimenti con Mappatura 3 in 1, 5500PasUltrasottile 32cm, 200min, Navigazione Laser dToF,</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GQVBWMN8?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GRV9WF91?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61a+kGiU4JL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61tT7fEMeqL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0GQVBWMN8</t>
+          <t>B0GRV9WF91</t>
         </is>
       </c>
       <c r="M37" s="1"/>
@@ -10059,14 +10015,12 @@
       <c r="W37" s="15"/>
       <c r="X37" s="15"/>
       <c r="Y37"/>
-      <c r="Z37" s="4">
-        <v>145</v>
-      </c>
+      <c r="Z37" s="4"/>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37"/>
       <c r="AD37" s="19">
-        <v>6468</v>
+        <v>2432</v>
       </c>
       <c r="AE37"/>
       <c r="AF37" s="20">
@@ -10122,7 +10076,7 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0GRV9WF91</t>
+          <t>B0GS64JBHY</t>
         </is>
       </c>
       <c r="D38" s="14"/>
@@ -10135,23 +10089,23 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Lefant M1 Robot Aspirapolvere Lavapavimenti con Mappatura 3 in 1, 5500PasUltrasottile 32cm, 200min, Navigazione Laser dToF,</t>
+          <t>ECOVACS T30e OMNI Robot Aspirapolvere Lavapavimenti 25000 PasZeroTangle Gen 3.0, spazzola later. ARClean, Spazzola Princip.</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GRV9WF91?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GS64JBHY?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61tT7fEMeqL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71pU2-QZ-hL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0GRV9WF91</t>
+          <t>B0GS64JBHY</t>
         </is>
       </c>
       <c r="M38" s="1"/>
@@ -10167,16 +10121,18 @@
       <c r="W38" s="15"/>
       <c r="X38" s="15"/>
       <c r="Y38"/>
-      <c r="Z38" s="4"/>
+      <c r="Z38" s="4">
+        <v>245.08</v>
+      </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38"/>
       <c r="AD38" s="19">
-        <v>2432</v>
+        <v>119</v>
       </c>
       <c r="AE38"/>
       <c r="AF38" s="20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG38" s="21">
         <v>0</v>
@@ -10228,7 +10184,7 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0GS64JBHY</t>
+          <t>B0GSRVQB6D</t>
         </is>
       </c>
       <c r="D39" s="14"/>
@@ -10241,23 +10197,23 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>ECOVACS T30e OMNI Robot Aspirapolvere Lavapavimenti 25000 PasZeroTangle Gen 3.0, spazzola later. ARClean, Spazzola Princip.</t>
+          <t>dreame L40 Ultra A Robot Aspirapolvere Lavapavimenti, Aspirazione 24.000 PasSpazzola TriCut, Sollevamento Mocio 10,5 mm, St</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GS64JBHY?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GSRVQB6D?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71pU2-QZ-hL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61IyIKglqdL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0GS64JBHY</t>
+          <t>B0GSRVQB6D</t>
         </is>
       </c>
       <c r="M39" s="1"/>
@@ -10273,18 +10229,16 @@
       <c r="W39" s="15"/>
       <c r="X39" s="15"/>
       <c r="Y39"/>
-      <c r="Z39" s="4">
-        <v>245.08</v>
-      </c>
+      <c r="Z39" s="4"/>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39"/>
       <c r="AD39" s="19">
-        <v>119</v>
+        <v>382</v>
       </c>
       <c r="AE39"/>
       <c r="AF39" s="20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG39" s="21">
         <v>0</v>
@@ -10336,7 +10290,7 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0GSRVQB6D</t>
+          <t>B0GSVGTK23</t>
         </is>
       </c>
       <c r="D40" s="14"/>
@@ -10349,23 +10303,23 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>dreame L40 Ultra A Robot Aspirapolvere Lavapavimenti, Aspirazione 24.000 PasSpazzola TriCut, Sollevamento Mocio 10,5 mm, St</t>
+          <t>Vexilar W8 Robot Aspirapolvere Lavapavimenti 8,000Pa 2,5 Ore, Silenzioso Aspirapolvere Robot Potente per Pavimenti/Tappeti,Co</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GSRVQB6D?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GSVGTK23?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61IyIKglqdL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81yFXDvfg3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0GSRVQB6D</t>
+          <t>B0GSVGTK23</t>
         </is>
       </c>
       <c r="M40" s="1"/>
@@ -10386,11 +10340,11 @@
       <c r="AB40"/>
       <c r="AC40"/>
       <c r="AD40" s="19">
-        <v>382</v>
+        <v>160</v>
       </c>
       <c r="AE40"/>
       <c r="AF40" s="20">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AG40" s="21">
         <v>0</v>
@@ -10442,7 +10396,7 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0GSVGTK23</t>
+          <t>B0GWJYLKPK</t>
         </is>
       </c>
       <c r="D41" s="14"/>
@@ -10455,23 +10409,23 @@
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Vexilar W8 Robot Aspirapolvere Lavapavimenti 8,000Pa 2,5 Ore, Silenzioso Aspirapolvere Robot Potente per Pavimenti/Tappeti,Co</t>
+          <t>MOVA Z70 Ultra Roller Complete Robot Aspirapolvere Powered by Dreames36.000 Pa e Design Antigroviglio, Spazzola E Rullo Est</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GSVGTK23?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GWJYLKPK?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81yFXDvfg3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71TiEBPzLxL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0GSVGTK23</t>
+          <t>B0GWJYLKPK</t>
         </is>
       </c>
       <c r="M41" s="1"/>
@@ -10492,11 +10446,11 @@
       <c r="AB41"/>
       <c r="AC41"/>
       <c r="AD41" s="19">
-        <v>160</v>
+        <v>35</v>
       </c>
       <c r="AE41"/>
       <c r="AF41" s="20">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AG41" s="21">
         <v>0</v>
@@ -10548,7 +10502,7 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0GWJYLKPK</t>
+          <t>B0GXW3NHKY</t>
         </is>
       </c>
       <c r="D42" s="14"/>
@@ -10561,23 +10515,23 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>MOVA Z70 Ultra Roller Complete Robot Aspirapolvere Powered by Dreames36.000 Pa e Design Antigroviglio, Spazzola E Rullo Est</t>
+          <t>MOVA dreame V70 Ultra Complete Robot Aspirapolvere, BiancosEstensione Mocio 17cm e Spazzola Laterale 12cm, 40.000Pa, Supera</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GWJYLKPK?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GXW3NHKY?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71TiEBPzLxL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61W5s1c6CzL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0GWJYLKPK</t>
+          <t>B0GXW3NHKY</t>
         </is>
       </c>
       <c r="M42" s="1"/>
@@ -10593,16 +10547,18 @@
       <c r="W42" s="15"/>
       <c r="X42" s="15"/>
       <c r="Y42"/>
-      <c r="Z42" s="4"/>
+      <c r="Z42" s="4">
+        <v>1063.09</v>
+      </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42"/>
       <c r="AD42" s="19">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="AE42"/>
       <c r="AF42" s="20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG42" s="21">
         <v>0</v>
@@ -10654,7 +10610,7 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0GXW3NHKY</t>
+          <t>B0GXWTH75T</t>
         </is>
       </c>
       <c r="D43" s="14"/>
@@ -10667,23 +10623,23 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>MOVA dreame V70 Ultra Complete Robot Aspirapolvere, BiancosEstensione Mocio 17cm e Spazzola Laterale 12cm, 40.000Pa, Supera</t>
+          <t>iRobot Roomba® Max 775 Combo robot aspirapolvere lavapavimenti, 30.000 PasCon stazione AutoWash™ autosvuotante, PowerSpin™</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GXW3NHKY?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GXWTH75T?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61W5s1c6CzL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71I1v-QWgOL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0GXW3NHKY</t>
+          <t>B0GXWTH75T</t>
         </is>
       </c>
       <c r="M43" s="1"/>
@@ -10700,17 +10656,17 @@
       <c r="X43" s="15"/>
       <c r="Y43"/>
       <c r="Z43" s="4">
-        <v>1063.09</v>
+        <v>613.93</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43"/>
       <c r="AD43" s="19">
-        <v>83</v>
+        <v>4030</v>
       </c>
       <c r="AE43"/>
       <c r="AF43" s="20">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG43" s="21">
         <v>0</v>
@@ -10762,7 +10718,7 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0GXWTH75T</t>
+          <t>B0GXWXK6VF</t>
         </is>
       </c>
       <c r="D44" s="14"/>
@@ -10775,23 +10731,23 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>iRobot Roomba® Max 775 Combo robot aspirapolvere lavapavimenti, 30.000 PasCon stazione AutoWash™ autosvuotante, PowerSpin™</t>
+          <t>iRobot Roomba® Plus 576 Combo robot aspirapolvere lavapavimenti, 25.000 PasCon stazione AutoWash™ autosvuotante lavaggio mo</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GXWTH75T?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GXWXK6VF?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71I1v-QWgOL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71DY4csxM0L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0GXWTH75T</t>
+          <t>B0GXWXK6VF</t>
         </is>
       </c>
       <c r="M44" s="1"/>
@@ -10808,17 +10764,17 @@
       <c r="X44" s="15"/>
       <c r="Y44"/>
       <c r="Z44" s="4">
-        <v>613.93</v>
+        <v>368.03</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44"/>
       <c r="AD44" s="19">
-        <v>4030</v>
+        <v>3557</v>
       </c>
       <c r="AE44"/>
       <c r="AF44" s="20">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AG44" s="21">
         <v>0</v>
@@ -10870,7 +10826,7 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0GXWXK6VF</t>
+          <t>B0GY89Y1G5</t>
         </is>
       </c>
       <c r="D45" s="14"/>
@@ -10883,23 +10839,23 @@
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>iRobot Roomba® Plus 576 Combo robot aspirapolvere lavapavimenti, 25.000 PasCon stazione AutoWash™ autosvuotante lavaggio mo</t>
+          <t>Vexilar Upgrade 10,000Pa Robot Aspirapolvere Lavapavimenti con Mappatura, 3 Ore, Silenzioso W9 Aspirapolvere Robot Lavapavime</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GXWXK6VF?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GY89Y1G5?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71DY4csxM0L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/716vSVzRMML._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0GXWXK6VF</t>
+          <t>B0GY89Y1G5</t>
         </is>
       </c>
       <c r="M45" s="1"/>
@@ -10915,18 +10871,16 @@
       <c r="W45" s="15"/>
       <c r="X45" s="15"/>
       <c r="Y45"/>
-      <c r="Z45" s="4">
-        <v>368.03</v>
-      </c>
+      <c r="Z45" s="4"/>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45"/>
       <c r="AD45" s="19">
-        <v>3557</v>
+        <v>130</v>
       </c>
       <c r="AE45"/>
       <c r="AF45" s="20">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AG45" s="21">
         <v>0</v>
@@ -10978,7 +10932,7 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0GY89Y1G5</t>
+          <t>B0GZZHY5MC</t>
         </is>
       </c>
       <c r="D46" s="14"/>
@@ -10991,23 +10945,23 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Vexilar Upgrade 10,000Pa Robot Aspirapolvere Lavapavimenti con Mappatura, 3 Ore, Silenzioso W9 Aspirapolvere Robot Lavapavime</t>
+          <t>roborock Qrevo 2 Pro Set Robot Aspirapolvere Lavapavimenti 25.000Pa, NerosPanno Estensibile, Antigroviglio, Autopulizia Pan</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GY89Y1G5?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GZZHY5MC?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/716vSVzRMML._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/6137mB7UtgL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0GY89Y1G5</t>
+          <t>B0GZZHY5MC</t>
         </is>
       </c>
       <c r="M46" s="1"/>
@@ -11028,11 +10982,11 @@
       <c r="AB46"/>
       <c r="AC46"/>
       <c r="AD46" s="19">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="AE46"/>
       <c r="AF46" s="20">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AG46" s="21">
         <v>0</v>
@@ -11084,7 +11038,7 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0GZZHY5MC</t>
+          <t>B0H2Q9XK94</t>
         </is>
       </c>
       <c r="D47" s="14"/>
@@ -11097,23 +11051,23 @@
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>roborock Qrevo 2 Pro Set Robot Aspirapolvere Lavapavimenti 25.000Pa, NerosPanno Estensibile, Antigroviglio, Autopulizia Pan</t>
+          <t>W23D Robot Lavavetri Elettrico, 6500 Pa Robot Lavavetri Automatico con Doppio Getto D'acqua, 3 Modalità, Navigazione Intellig</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GZZHY5MC?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H2Q9XK94?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/6137mB7UtgL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71I-iLl7gPL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0GZZHY5MC</t>
+          <t>B0H2Q9XK94</t>
         </is>
       </c>
       <c r="M47" s="1"/>
@@ -11134,11 +11088,11 @@
       <c r="AB47"/>
       <c r="AC47"/>
       <c r="AD47" s="19">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="AE47"/>
       <c r="AF47" s="20">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AG47" s="21">
         <v>0</v>
@@ -11190,7 +11144,7 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0H2Q9XK94</t>
+          <t>B0H3TRY2PP</t>
         </is>
       </c>
       <c r="D48" s="14"/>
@@ -11203,23 +11157,23 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>W23D Robot Lavavetri Elettrico, 6500 Pa Robot Lavavetri Automatico con Doppio Getto D'acqua, 3 Modalità, Navigazione Intellig</t>
+          <t>IERAKOR Robot Lavavetri Elettrico, Pulisci Vetri Automatico 5600PasDoppio Spruzzo D'Acqua, 3 Modalità, Navigazione Intellig</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H2Q9XK94?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H3TRY2PP?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71I-iLl7gPL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61KY9cQuvTL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0H2Q9XK94</t>
+          <t>B0H3TRY2PP</t>
         </is>
       </c>
       <c r="M48" s="1"/>
@@ -11240,11 +11194,11 @@
       <c r="AB48"/>
       <c r="AC48"/>
       <c r="AD48" s="19">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AE48"/>
       <c r="AF48" s="20">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AG48" s="21">
         <v>0</v>
@@ -11296,7 +11250,7 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0H3TRY2PP</t>
+          <t>B0H419WWBZ</t>
         </is>
       </c>
       <c r="D49" s="14"/>
@@ -11309,23 +11263,23 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>IERAKOR Robot Lavavetri Elettrico, Pulisci Vetri Automatico 5600PasDoppio Spruzzo D'Acqua, 3 Modalità, Navigazione Intellig</t>
+          <t>roborock Saros 20 Neo Robot Aspirapolvere Lavapavimenti con LDS Retrattiles7,95cm, 36.000Pa, Supera Ostacoli da 8,8cm, Anti</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H3TRY2PP?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H419WWBZ?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61KY9cQuvTL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51k1SMqcZML._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0H3TRY2PP</t>
+          <t>B0H419WWBZ</t>
         </is>
       </c>
       <c r="M49" s="1"/>
@@ -11346,11 +11300,11 @@
       <c r="AB49"/>
       <c r="AC49"/>
       <c r="AD49" s="19">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AE49"/>
       <c r="AF49" s="20">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AG49" s="21">
         <v>0</v>
@@ -11402,7 +11356,7 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0H419WWBZ</t>
+          <t>B0H9RNX24M</t>
         </is>
       </c>
       <c r="D50" s="14"/>
@@ -11415,23 +11369,23 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>roborock Saros 20 Neo Robot Aspirapolvere Lavapavimenti con LDS Retrattiles7,95cm, 36.000Pa, Supera Ostacoli da 8,8cm, Anti</t>
+          <t>ECOVACS T90 MAX PRO Robot Aspirapolvere Lavapavimenti 40.000 PasOZMO ROLLER 3.0, Lavaggio auto., ZeroTangle 4.0 con TruEdge</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H419WWBZ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H9RNX24M?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51k1SMqcZML._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71OJGGx7o5L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0H419WWBZ</t>
+          <t>B0H9RNX24M</t>
         </is>
       </c>
       <c r="M50" s="1"/>
@@ -11452,11 +11406,11 @@
       <c r="AB50"/>
       <c r="AC50"/>
       <c r="AD50" s="19">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="AE50"/>
       <c r="AF50" s="20">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AG50" s="21">
         <v>0</v>
@@ -11501,112 +11455,6 @@
       <c r="BQ50" s="22"/>
       <c r="BR50"/>
     </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0H9RNX24M</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.itundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>ECOVACS T90 MAX PRO Robot Aspirapolvere Lavapavimenti 40.000 PasOZMO ROLLER 3.0, Lavaggio auto., ZeroTangle 4.0 con TruEdge</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0H9RNX24M?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71OJGGx7o5L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0H9RNX24M</t>
-        </is>
-      </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51" s="19">
-        <v>6</v>
-      </c>
-      <c r="AE51"/>
-      <c r="AF51" s="20">
-        <v>5</v>
-      </c>
-      <c r="AG51" s="21">
-        <v>0</v>
-      </c>
-      <c r="AH51"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
-      <c r="BK51" s="22"/>
-      <c r="BL51"/>
-      <c r="BM51" s="22"/>
-      <c r="BN51"/>
-      <c r="BO51" s="22"/>
-      <c r="BP51"/>
-      <c r="BQ51" s="22"/>
-      <c r="BR51"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -11616,253 +11464,248 @@
     <hyperlink ref="J2" r:id="rId3" tooltip="https://www.amazon.it/dp/B0BLNJ5WH3?psc=1"/>
     <hyperlink ref="K2" r:id="rId4" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41CbAbftq5L._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.it/dp/B0BLNJ5WH3"/>
-    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.it/dp/B0C78DVSYP"/>
+    <hyperlink ref="C3" r:id="rId6" tooltip="https://www.amazon.it/dp/B0CTCXKL52"/>
     <hyperlink ref="G3" r:id="rId7" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.it/dp/B0C78DVSYP?psc=1"/>
-    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71wCGkM+anL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.it/dp/B0C78DVSYP"/>
-    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.it/dp/B0CTCXKL52"/>
+    <hyperlink ref="J3" r:id="rId8" tooltip="https://www.amazon.it/dp/B0CTCXKL52?psc=1"/>
+    <hyperlink ref="K3" r:id="rId9" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61+Y7BWWOlL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L3" r:id="rId10" tooltip="https://www.amazon.it/dp/B0CTCXKL52"/>
+    <hyperlink ref="C4" r:id="rId11" tooltip="https://www.amazon.it/dp/B0DGQVLY99"/>
     <hyperlink ref="G4" r:id="rId12" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.it/dp/B0CTCXKL52?psc=1"/>
-    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61+Y7BWWOlL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.it/dp/B0CTCXKL52"/>
-    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.it/dp/B0DGQVLY99"/>
+    <hyperlink ref="J4" r:id="rId13" tooltip="https://www.amazon.it/dp/B0DGQVLY99?psc=1"/>
+    <hyperlink ref="K4" r:id="rId14" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RZtXsJInL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L4" r:id="rId15" tooltip="https://www.amazon.it/dp/B0DGQVLY99"/>
+    <hyperlink ref="C5" r:id="rId16" tooltip="https://www.amazon.it/dp/B0DHKM58LV"/>
     <hyperlink ref="G5" r:id="rId17" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.it/dp/B0DGQVLY99?psc=1"/>
-    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RZtXsJInL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.it/dp/B0DGQVLY99"/>
-    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.it/dp/B0DHKM58LV"/>
+    <hyperlink ref="J5" r:id="rId18" tooltip="https://www.amazon.it/dp/B0DHKM58LV?psc=1"/>
+    <hyperlink ref="K5" r:id="rId19" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71jEf9a4LnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L5" r:id="rId20" tooltip="https://www.amazon.it/dp/B0DHKM58LV"/>
+    <hyperlink ref="C6" r:id="rId21" tooltip="https://www.amazon.it/dp/B0DPB7RN2L"/>
     <hyperlink ref="G6" r:id="rId22" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.it/dp/B0DHKM58LV?psc=1"/>
-    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71jEf9a4LnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.it/dp/B0DHKM58LV"/>
-    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.it/dp/B0DPB7RN2L"/>
+    <hyperlink ref="J6" r:id="rId23" tooltip="https://www.amazon.it/dp/B0DPB7RN2L?psc=1"/>
+    <hyperlink ref="K6" r:id="rId24" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71uia0AyolL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L6" r:id="rId25" tooltip="https://www.amazon.it/dp/B0DPB7RN2L"/>
+    <hyperlink ref="C7" r:id="rId26" tooltip="https://www.amazon.it/dp/B0DPZTS99T"/>
     <hyperlink ref="G7" r:id="rId27" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.it/dp/B0DPB7RN2L?psc=1"/>
-    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71uia0AyolL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.it/dp/B0DPB7RN2L"/>
-    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.it/dp/B0DPZTS99T"/>
+    <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.it/dp/B0DPZTS99T?psc=1"/>
+    <hyperlink ref="K7" r:id="rId29" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61h0GDNMI4L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.it/dp/B0DPZTS99T"/>
+    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.it/dp/B0DSZXC512"/>
     <hyperlink ref="G8" r:id="rId32" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.it/dp/B0DPZTS99T?psc=1"/>
-    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61h0GDNMI4L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.it/dp/B0DPZTS99T"/>
-    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.it/dp/B0DSZXC512"/>
+    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.it/dp/B0DSZXC512?psc=1"/>
+    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61DA4yhQb2L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.it/dp/B0DSZXC512"/>
+    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.it/dp/B0DV9TBKM1"/>
     <hyperlink ref="G9" r:id="rId37" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.it/dp/B0DSZXC512?psc=1"/>
-    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61DA4yhQb2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.it/dp/B0DSZXC512"/>
-    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.it/dp/B0DV9TBKM1"/>
+    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.it/dp/B0DV9TBKM1?psc=1"/>
+    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ge+TRWY0L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.it/dp/B0DV9TBKM1"/>
+    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.it/dp/B0DWK8GJZX"/>
     <hyperlink ref="G10" r:id="rId42" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.it/dp/B0DV9TBKM1?psc=1"/>
-    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ge+TRWY0L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.it/dp/B0DV9TBKM1"/>
-    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.it/dp/B0DWK8GJZX"/>
+    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.it/dp/B0DWK8GJZX?psc=1"/>
+    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-eu.ssl-images-amazon.com/images/I/518ZZDibQUL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.it/dp/B0DWK8GJZX"/>
+    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.it/dp/B0DZ64GW9Z"/>
     <hyperlink ref="G11" r:id="rId47" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.it/dp/B0DWK8GJZX?psc=1"/>
-    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/518ZZDibQUL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.it/dp/B0DWK8GJZX"/>
-    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.it/dp/B0DZ64GW9Z"/>
+    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.it/dp/B0DZ64GW9Z?psc=1"/>
+    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61DTY2iTgGL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.it/dp/B0DZ64GW9Z"/>
+    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.it/dp/B0F4JZNGT8"/>
     <hyperlink ref="G12" r:id="rId52" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.it/dp/B0DZ64GW9Z?psc=1"/>
-    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61DTY2iTgGL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.it/dp/B0DZ64GW9Z"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.it/dp/B0F4JZNGT8"/>
+    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.it/dp/B0F4JZNGT8?psc=1"/>
+    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61h6FZILm2L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.it/dp/B0F4JZNGT8"/>
+    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.it/dp/B0F53MJY8T"/>
     <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.it/dp/B0F4JZNGT8?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61h6FZILm2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.it/dp/B0F4JZNGT8"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.it/dp/B0F53MJY8T"/>
+    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.it/dp/B0F53MJY8T?psc=1"/>
+    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Oewwp7QtL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.it/dp/B0F53MJY8T"/>
+    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.it/dp/B0FBG6V2LG"/>
     <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.it/dp/B0F53MJY8T?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Oewwp7QtL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.it/dp/B0F53MJY8T"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.it/dp/B0FBG6V2LG"/>
+    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.it/dp/B0FBG6V2LG?psc=1"/>
+    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Du2Zv+GrL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.it/dp/B0FBG6V2LG"/>
+    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.it/dp/B0FBGXW79K"/>
     <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.it/dp/B0FBG6V2LG?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Du2Zv+GrL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.it/dp/B0FBG6V2LG"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.it/dp/B0FBGXW79K"/>
+    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.it/dp/B0FBGXW79K?psc=1"/>
+    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61AWpU4EwAL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.it/dp/B0FBGXW79K"/>
+    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.it/dp/B0FC2VSX1R"/>
     <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.it/dp/B0FBGXW79K?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61AWpU4EwAL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.it/dp/B0FBGXW79K"/>
-    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.it/dp/B0FC2VSX1R"/>
+    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.it/dp/B0FC2VSX1R?psc=1"/>
+    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Sp5FUK9FL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.it/dp/B0FC2VSX1R"/>
+    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.it/dp/B0FDLDM33M"/>
     <hyperlink ref="G17" r:id="rId77" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.it/dp/B0FC2VSX1R?psc=1"/>
-    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Sp5FUK9FL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.it/dp/B0FC2VSX1R"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.it/dp/B0FDLDM33M"/>
+    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.it/dp/B0FDLDM33M?psc=1"/>
+    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61PLSniytTL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.it/dp/B0FDLDM33M"/>
+    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.it/dp/B0FFGQ7L2T"/>
     <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.it/dp/B0FDLDM33M?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61PLSniytTL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.it/dp/B0FDLDM33M"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.it/dp/B0FFGQ7L2T"/>
+    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.it/dp/B0FFGQ7L2T?psc=1"/>
+    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61lhiSiiW9L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.it/dp/B0FFGQ7L2T"/>
+    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.it/dp/B0FHHYQ58Q"/>
     <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.it/dp/B0FFGQ7L2T?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61lhiSiiW9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.it/dp/B0FFGQ7L2T"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.it/dp/B0FHHYQ58Q"/>
+    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.it/dp/B0FHHYQ58Q?psc=1"/>
+    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/719E8Elku9L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.it/dp/B0FHHYQ58Q"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.it/dp/B0FHWP5Y6P"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.it/dp/B0FHHYQ58Q?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/719E8Elku9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.it/dp/B0FHHYQ58Q"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.it/dp/B0FHWP5Y6P"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.it/dp/B0FHWP5Y6P?psc=1"/>
+    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81n8UEz9tuL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.it/dp/B0FHWP5Y6P"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.it/dp/B0FL2JGPYH"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.it/dp/B0FHWP5Y6P?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81n8UEz9tuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.it/dp/B0FHWP5Y6P"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.it/dp/B0FL2JGPYH"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.it/dp/B0FL2JGPYH?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/9189DpGCbIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.it/dp/B0FL2JGPYH"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.it/dp/B0FNWFTJKQ"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.it/dp/B0FL2JGPYH?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/9189DpGCbIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.it/dp/B0FL2JGPYH"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.it/dp/B0FNWFTJKQ"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.it/dp/B0FNWFTJKQ?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61R08mDJ-PL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.it/dp/B0FNWFTJKQ"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.it/dp/B0FXXCFT8Z"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.it/dp/B0FNWFTJKQ?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61R08mDJ-PL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.it/dp/B0FNWFTJKQ"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.it/dp/B0FXXCFT8Z"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.it/dp/B0FXXCFT8Z?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71apWwSX4-L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.it/dp/B0FXXCFT8Z"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.it/dp/B0G4NBBZLG"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.it/dp/B0FXXCFT8Z?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71apWwSX4-L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.it/dp/B0FXXCFT8Z"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.it/dp/B0G4NBBZLG"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.it/dp/B0G4NBBZLG?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61575fRbYFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.it/dp/B0G4NBBZLG"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.it/dp/B0G81F3HSR"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.it/dp/B0G4NBBZLG?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61575fRbYFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.it/dp/B0G4NBBZLG"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.it/dp/B0G81F3HSR"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.it/dp/B0G81F3HSR?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71FDvNkpTPL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.it/dp/B0G81F3HSR"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.it/dp/B0GHN9DR1C"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.it/dp/B0G81F3HSR?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71FDvNkpTPL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.it/dp/B0G81F3HSR"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.it/dp/B0GHN9DR1C"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.it/dp/B0GHN9DR1C?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Sk4jG6C4L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.it/dp/B0GHN9DR1C"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.it/dp/B0GJRWS8BQ"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.it/dp/B0GHN9DR1C?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Sk4jG6C4L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.it/dp/B0GHN9DR1C"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.it/dp/B0GJRWS8BQ"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.it/dp/B0GJRWS8BQ?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+HO6GsuVL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.it/dp/B0GJRWS8BQ"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.it/dp/B0GK1RD2T7"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.it/dp/B0GJRWS8BQ?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+HO6GsuVL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.it/dp/B0GJRWS8BQ"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.it/dp/B0GK1RD2T7"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.it/dp/B0GK1RD2T7?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81cXtuIXJ2L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.it/dp/B0GK1RD2T7"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.it/dp/B0GKFK2L1M"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.it/dp/B0GK1RD2T7?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81cXtuIXJ2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.it/dp/B0GK1RD2T7"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.it/dp/B0GKFK2L1M"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.it/dp/B0GKFK2L1M?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xscdGZwKL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.it/dp/B0GKFK2L1M"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.it/dp/B0GLNVNGHJ"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.it/dp/B0GKFK2L1M?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71xscdGZwKL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.it/dp/B0GKFK2L1M"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.it/dp/B0GLNVNGHJ"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.it/dp/B0GLNVNGHJ?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Nj3cHYNTL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.it/dp/B0GLNVNGHJ"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.it/dp/B0GMHC87FB"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.it/dp/B0GLNVNGHJ?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Nj3cHYNTL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.it/dp/B0GLNVNGHJ"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.it/dp/B0GMHC87FB"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.it/dp/B0GMHC87FB?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GibzcMLqL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.it/dp/B0GMHC87FB"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.it/dp/B0GMKFQ78D"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.it/dp/B0GMHC87FB?psc=1"/>
-    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GibzcMLqL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.it/dp/B0GMHC87FB"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.it/dp/B0GMKFQ78D"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.it/dp/B0GMKFQ78D?psc=1"/>
+    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/31LHrNdbtZL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.it/dp/B0GMKFQ78D"/>
+    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.it/dp/B0GQFK3DD5"/>
     <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.it/dp/B0GMKFQ78D?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/31LHrNdbtZL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.it/dp/B0GMKFQ78D"/>
-    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.it/dp/B0GQFK3DD5"/>
+    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.it/dp/B0GQFK3DD5?psc=1"/>
+    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71WcgmlpUtL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.it/dp/B0GQFK3DD5"/>
+    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.it/dp/B0GQHBTNP8"/>
     <hyperlink ref="G34" r:id="rId162" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.it/dp/B0GQFK3DD5?psc=1"/>
-    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71WcgmlpUtL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.it/dp/B0GQFK3DD5"/>
-    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.it/dp/B0GQHBTNP8"/>
+    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.it/dp/B0GQHBTNP8?psc=1"/>
+    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/8172iDMPT7L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.it/dp/B0GQHBTNP8"/>
+    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.it/dp/B0GQT9CQ17"/>
     <hyperlink ref="G35" r:id="rId167" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.it/dp/B0GQHBTNP8?psc=1"/>
-    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/8172iDMPT7L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.it/dp/B0GQHBTNP8"/>
-    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.it/dp/B0GQT9CQ17"/>
+    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.it/dp/B0GQT9CQ17?psc=1"/>
+    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6146vF3XIXL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.it/dp/B0GQT9CQ17"/>
+    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.it/dp/B0GQVBWMN8"/>
     <hyperlink ref="G36" r:id="rId172" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.it/dp/B0GQT9CQ17?psc=1"/>
-    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6146vF3XIXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.it/dp/B0GQT9CQ17"/>
-    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.it/dp/B0GQVBWMN8"/>
+    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.it/dp/B0GQVBWMN8?psc=1"/>
+    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61a+kGiU4JL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.it/dp/B0GQVBWMN8"/>
+    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.it/dp/B0GRV9WF91"/>
     <hyperlink ref="G37" r:id="rId177" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.it/dp/B0GQVBWMN8?psc=1"/>
-    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61a+kGiU4JL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.it/dp/B0GQVBWMN8"/>
-    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.it/dp/B0GRV9WF91"/>
+    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.it/dp/B0GRV9WF91?psc=1"/>
+    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tT7fEMeqL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.it/dp/B0GRV9WF91"/>
+    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.it/dp/B0GS64JBHY"/>
     <hyperlink ref="G38" r:id="rId182" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.it/dp/B0GRV9WF91?psc=1"/>
-    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tT7fEMeqL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.it/dp/B0GRV9WF91"/>
-    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.it/dp/B0GS64JBHY"/>
+    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.it/dp/B0GS64JBHY?psc=1"/>
+    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pU2-QZ-hL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.it/dp/B0GS64JBHY"/>
+    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.it/dp/B0GSRVQB6D"/>
     <hyperlink ref="G39" r:id="rId187" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.it/dp/B0GS64JBHY?psc=1"/>
-    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pU2-QZ-hL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.it/dp/B0GS64JBHY"/>
-    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.it/dp/B0GSRVQB6D"/>
+    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.it/dp/B0GSRVQB6D?psc=1"/>
+    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61IyIKglqdL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.it/dp/B0GSRVQB6D"/>
+    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.it/dp/B0GSVGTK23"/>
     <hyperlink ref="G40" r:id="rId192" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.it/dp/B0GSRVQB6D?psc=1"/>
-    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61IyIKglqdL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.it/dp/B0GSRVQB6D"/>
-    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.it/dp/B0GSVGTK23"/>
+    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.it/dp/B0GSVGTK23?psc=1"/>
+    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81yFXDvfg3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.it/dp/B0GSVGTK23"/>
+    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.it/dp/B0GWJYLKPK"/>
     <hyperlink ref="G41" r:id="rId197" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.it/dp/B0GSVGTK23?psc=1"/>
-    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81yFXDvfg3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.it/dp/B0GSVGTK23"/>
-    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.it/dp/B0GWJYLKPK"/>
+    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.it/dp/B0GWJYLKPK?psc=1"/>
+    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TiEBPzLxL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.it/dp/B0GWJYLKPK"/>
+    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.it/dp/B0GXW3NHKY"/>
     <hyperlink ref="G42" r:id="rId202" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.it/dp/B0GWJYLKPK?psc=1"/>
-    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TiEBPzLxL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.it/dp/B0GWJYLKPK"/>
-    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.it/dp/B0GXW3NHKY"/>
+    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.it/dp/B0GXW3NHKY?psc=1"/>
+    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61W5s1c6CzL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.it/dp/B0GXW3NHKY"/>
+    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.it/dp/B0GXWTH75T"/>
     <hyperlink ref="G43" r:id="rId207" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.it/dp/B0GXW3NHKY?psc=1"/>
-    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61W5s1c6CzL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.it/dp/B0GXW3NHKY"/>
-    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.it/dp/B0GXWTH75T"/>
+    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.it/dp/B0GXWTH75T?psc=1"/>
+    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71I1v-QWgOL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.it/dp/B0GXWTH75T"/>
+    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.it/dp/B0GXWXK6VF"/>
     <hyperlink ref="G44" r:id="rId212" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.it/dp/B0GXWTH75T?psc=1"/>
-    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71I1v-QWgOL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.it/dp/B0GXWTH75T"/>
-    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.it/dp/B0GXWXK6VF"/>
+    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.it/dp/B0GXWXK6VF?psc=1"/>
+    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71DY4csxM0L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.it/dp/B0GXWXK6VF"/>
+    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.it/dp/B0GY89Y1G5"/>
     <hyperlink ref="G45" r:id="rId217" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.it/dp/B0GXWXK6VF?psc=1"/>
-    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71DY4csxM0L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.it/dp/B0GXWXK6VF"/>
-    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.it/dp/B0GY89Y1G5"/>
+    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.it/dp/B0GY89Y1G5?psc=1"/>
+    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-eu.ssl-images-amazon.com/images/I/716vSVzRMML._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.it/dp/B0GY89Y1G5"/>
+    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.it/dp/B0GZZHY5MC"/>
     <hyperlink ref="G46" r:id="rId222" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.it/dp/B0GY89Y1G5?psc=1"/>
-    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-eu.ssl-images-amazon.com/images/I/716vSVzRMML._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.it/dp/B0GY89Y1G5"/>
-    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.it/dp/B0GZZHY5MC"/>
+    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.it/dp/B0GZZHY5MC?psc=1"/>
+    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6137mB7UtgL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.it/dp/B0GZZHY5MC"/>
+    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.it/dp/B0H2Q9XK94"/>
     <hyperlink ref="G47" r:id="rId227" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.it/dp/B0GZZHY5MC?psc=1"/>
-    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6137mB7UtgL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.it/dp/B0GZZHY5MC"/>
-    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.it/dp/B0H2Q9XK94"/>
+    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.it/dp/B0H2Q9XK94?psc=1"/>
+    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71I-iLl7gPL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.it/dp/B0H2Q9XK94"/>
+    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.it/dp/B0H3TRY2PP"/>
     <hyperlink ref="G48" r:id="rId232" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.it/dp/B0H2Q9XK94?psc=1"/>
-    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71I-iLl7gPL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.it/dp/B0H2Q9XK94"/>
-    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.it/dp/B0H3TRY2PP"/>
+    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.it/dp/B0H3TRY2PP?psc=1"/>
+    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61KY9cQuvTL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.it/dp/B0H3TRY2PP"/>
+    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.it/dp/B0H419WWBZ"/>
     <hyperlink ref="G49" r:id="rId237" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.it/dp/B0H3TRY2PP?psc=1"/>
-    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61KY9cQuvTL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.it/dp/B0H3TRY2PP"/>
-    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.it/dp/B0H419WWBZ"/>
+    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.it/dp/B0H419WWBZ?psc=1"/>
+    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51k1SMqcZML._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.it/dp/B0H419WWBZ"/>
+    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.it/dp/B0H9RNX24M"/>
     <hyperlink ref="G50" r:id="rId242" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.it/dp/B0H419WWBZ?psc=1"/>
-    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51k1SMqcZML._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.it/dp/B0H419WWBZ"/>
-    <hyperlink ref="C51" r:id="rId246" tooltip="https://www.amazon.it/dp/B0H9RNX24M"/>
-    <hyperlink ref="G51" r:id="rId247" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J51" r:id="rId248" tooltip="https://www.amazon.it/dp/B0H9RNX24M?psc=1"/>
-    <hyperlink ref="K51" r:id="rId249" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71OJGGx7o5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId250" tooltip="https://www.amazon.it/dp/B0H9RNX24M"/>
+    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.it/dp/B0H9RNX24M?psc=1"/>
+    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71OJGGx7o5L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.it/dp/B0H9RNX24M"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId246"/>
 </worksheet>
 </file>
 
